--- a/healthcare_surveys/039_health_symptoms_questionnaire--healthcare_surveys.xlsx
+++ b/healthcare_surveys/039_health_symptoms_questionnaire--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>symptom_category</t>
+          <t>general_symptoms</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Symptoms</t>
+          <t>General Symptoms</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -589,7 +589,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>symptom_2</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Additional Information (2)</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,92 +676,92 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>email_2</t>
+          <t>time</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Email (2)</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Fever</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>nausea</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Nausea</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -773,315 +773,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>symptom_3</t>
+          <t>chills</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fever</t>
+          <t>Chills</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>symptom_4</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nausea</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>date_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Date (2)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>symptom_5</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Chills</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>symptom_6</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Cough</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>symptom_7</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Nausea</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>email_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Email (3)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>symptom_8</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Fatigue</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>symptom_9</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Fatigue</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>symptom_10</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Cough</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>symptom_11</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Fatigue</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>symptom_12</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Fatigue</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>symptom_13</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Nausea</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>symptom_14</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Fatigue</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,51 +827,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>symptom_category_choices</t>
+          <t>general_symptoms_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'general_symptoms',_'label':_'general_symptoms'}</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'General Symptoms', 'label': 'General Symptoms'}</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>symptom_category_choices</t>
+          <t>general_symptoms_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'neurological_symptoms',_'label':_'neurological_symptoms'}</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Neurological Symptoms', 'label': 'Neurological Symptoms'}</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>symptom_category_choices</t>
+          <t>pain_location_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'musculoskeletal_symptoms',_'label':_'musculoskeletal_symptoms'}</t>
+          <t>head</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Musculoskeletal Symptoms', 'label': 'Musculoskeletal Symptoms'}</t>
+          <t>Head</t>
         </is>
       </c>
     </row>
@@ -1182,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'head',_'label':_'head'}</t>
+          <t>neck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Head', 'label': 'Head'}</t>
+          <t>Neck</t>
         </is>
       </c>
     </row>
@@ -1199,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'neck',_'label':_'neck'}</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Neck', 'label': 'Neck'}</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
@@ -1216,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'back',_'label':_'back'}</t>
+          <t>stomach</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Back', 'label': 'Back'}</t>
+          <t>Stomach</t>
         </is>
       </c>
     </row>
@@ -1233,29 +934,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'stomach',_'label':_'stomach'}</t>
+          <t>legs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Stomach', 'label': 'Stomach'}</t>
+          <t>Legs</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pain_location_choices</t>
+          <t>symptom_1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'legs',_'label':_'legs'}</t>
+          <t>cough</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Legs', 'label': 'Legs'}</t>
+          <t>Cough</t>
         </is>
       </c>
     </row>
@@ -1267,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'cough',_'label':_'cough'}</t>
+          <t>coughing_up_blood</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Cough', 'label': 'Cough'}</t>
+          <t>Coughing Up Blood</t>
         </is>
       </c>
     </row>
@@ -1284,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'coughing_up_blood',_'label':_'coughing_up_blood'}</t>
+          <t>chest_pain</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Coughing Up Blood', 'label': 'Coughing Up Blood'}</t>
+          <t>Chest Pain</t>
         </is>
       </c>
     </row>
@@ -1301,743 +1002,148 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'chest_pain',_'label':_'chest_pain'}</t>
+          <t>shortness_of_breath</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Chest Pain', 'label': 'Chest Pain'}</t>
+          <t>Shortness of Breath</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>symptom_1_choices</t>
+          <t>fatigue_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'shortness_of_breath',_'label':_'shortness_of_breath'}</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Shortness of Breath', 'label': 'Shortness of Breath'}</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>symptom_2_choices</t>
+          <t>fatigue_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'fatigue',_'label':_'fatigue'}</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Fatigue', 'label': 'Fatigue'}</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>symptom_2_choices</t>
+          <t>fever_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'fatigue',_'label':_'fatigue'}</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Fatigue', 'label': 'Fatigue'}</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>symptom_2_choices</t>
+          <t>fever_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'fatigue',_'label':_'fatigue'}</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Fatigue', 'label': 'Fatigue'}</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>symptom_3_choices</t>
+          <t>nausea_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'fever',_'label':_'fever'}</t>
+          <t>nausea</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Fever', 'label': 'Fever'}</t>
+          <t>Nausea</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>symptom_3_choices</t>
+          <t>nausea_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'fever',_'label':_'fever'}</t>
+          <t>vomiting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Fever', 'label': 'Fever'}</t>
+          <t>Vomiting</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>symptom_3_choices</t>
+          <t>chills_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'fever',_'label':_'fever'}</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Fever', 'label': 'Fever'}</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>symptom_3_choices</t>
+          <t>chills_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'fever',_'label':_'fever'}</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Fever', 'label': 'Fever'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>symptom_3_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'value':_'fever',_'label':_'fever'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'value': 'Fever', 'label': 'Fever'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>symptom_4_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'value':_'nausea',_'label':_'nausea'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'value': 'Nausea', 'label': 'Nausea'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>symptom_4_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'value':_'vomiting',_'label':_'vomiting'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'value': 'Vomiting', 'label': 'Vomiting'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>symptom_4_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'value':_'diarrhea',_'label':_'diarrhea'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'value': 'Diarrhea', 'label': 'Diarrhea'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>symptom_5_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'value':_'chills',_'label':_'chills'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'value': 'Chills', 'label': 'Chills'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>symptom_5_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'value':_'chills',_'label':_'chills'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'value': 'Chills', 'label': 'Chills'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>symptom_5_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'value':_'chills',_'label':_'chills'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'value': 'Chills', 'label': 'Chills'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>symptom_5_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'value':_'chills',_'label':_'chills'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'value': 'Chills', 'label': 'Chills'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>symptom_6_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'value':_'cough',_'label':_'cough'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'value': 'Cough', 'label': 'Cough'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>symptom_6_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'value':_'cough',_'label':_'cough'}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'value': 'Cough', 'label': 'Cough'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>symptom_7_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'value':_'nausea',_'label':_'nausea'}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'value': 'Nausea', 'label': 'Nausea'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>symptom_7_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'value':_'nausea',_'label':_'nausea'}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'value': 'Nausea', 'label': 'Nausea'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>symptom_7_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'value':_'nausea',_'label':_'nausea'}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'value': 'Nausea', 'label': 'Nausea'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>symptom_7_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'value':_'vomiting',_'label':_'vomiting'}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'value': 'Vomiting', 'label': 'Vomiting'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>symptom_8_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'value':_'fatigue',_'label':_'fatigue'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'value': 'Fatigue', 'label': 'Fatigue'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>symptom_8_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'value':_'fatigue',_'label':_'fatigue'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'value': 'Fatigue', 'label': 'Fatigue'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>symptom_9_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'value':_'fatigue',_'label':_'fatigue'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'value': 'Fatigue', 'label': 'Fatigue'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>symptom_9_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'value':_'fatigue',_'label':_'fatigue'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'value': 'Fatigue', 'label': 'Fatigue'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>symptom_9_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'value':_'fatigue',_'label':_'fatigue'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'value': 'Fatigue', 'label': 'Fatigue'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>symptom_10_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'value':_'cough',_'label':_'cough'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'value': 'Cough', 'label': 'Cough'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>symptom_10_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'value':_'cough',_'label':_'cough'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'value': 'Cough', 'label': 'Cough'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>symptom_10_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'value':_'cough',_'label':_'cough'}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'value': 'Cough', 'label': 'Cough'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>symptom_11_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>{'value':_'fatigue',_'label':_'fatigue'}</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>{'value': 'Fatigue', 'label': 'Fatigue'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>symptom_11_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>{'value':_'fatigue',_'label':_'fatigue'}</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>{'value': 'Fatigue', 'label': 'Fatigue'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>symptom_11_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>{'value':_'fatigue',_'label':_'fatigue'}</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>{'value': 'Fatigue', 'label': 'Fatigue'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>symptom_11_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>{'value':_'fatigue',_'label':_'fatigue'}</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>{'value': 'Fatigue', 'label': 'Fatigue'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>symptom_12_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>{'value':_'fatigue',_'label':_'fatigue'}</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>{'value': 'Fatigue', 'label': 'Fatigue'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>symptom_12_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>{'value':_'fatigue',_'label':_'fatigue'}</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>{'value': 'Fatigue', 'label': 'Fatigue'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>symptom_12_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>{'value':_'fatigue',_'label':_'fatigue'}</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>{'value': 'Fatigue', 'label': 'Fatigue'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>symptom_13_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>{'value':_'nausea',_'label':_'nausea'}</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>{'value': 'Nausea', 'label': 'Nausea'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>symptom_13_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>{'value':_'nausea',_'label':_'nausea'}</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>{'value': 'Nausea', 'label': 'Nausea'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>symptom_13_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>{'value':_'nausea',_'label':_'nausea'}</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>{'value': 'Nausea', 'label': 'Nausea'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>symptom_14_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>{'value':_'fatigue',_'label':_'fatigue'}</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>{'value': 'Fatigue', 'label': 'Fatigue'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>symptom_14_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>{'value':_'fatigue',_'label':_'fatigue'}</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>{'value': 'Fatigue', 'label': 'Fatigue'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>symptom_14_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>{'value':_'fatigue',_'label':_'fatigue'}</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>{'value': 'Fatigue', 'label': 'Fatigue'}</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
